--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D3">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>426</v>
